--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.86796</v>
+        <v>17.21002</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77758</v>
+        <v>16.70238</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77049</v>
+        <v>16.75388</v>
       </c>
       <c r="F2" t="n">
-        <v>42.9771</v>
+        <v>43.34265</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05065</v>
+        <v>0.05006</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81827</v>
+        <v>1.85081</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.16306</v>
+        <v>17.16885</v>
       </c>
       <c r="D3" t="n">
-        <v>16.91817</v>
+        <v>16.80299</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81098</v>
+        <v>16.92836</v>
       </c>
       <c r="F3" t="n">
-        <v>43.35811</v>
+        <v>43.41051</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05116</v>
+        <v>0.05074</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81092</v>
+        <v>1.87896</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.16466</v>
+        <v>16.92729</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59872</v>
+        <v>16.78094</v>
       </c>
       <c r="E4" t="n">
-        <v>17.29457</v>
+        <v>16.88202</v>
       </c>
       <c r="F4" t="n">
-        <v>43.1401</v>
+        <v>42.79554</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05118</v>
+        <v>0.05085</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83433</v>
+        <v>1.8463</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.86631</v>
+        <v>17.11751</v>
       </c>
       <c r="D6" t="n">
-        <v>15.88688</v>
+        <v>16.05195</v>
       </c>
       <c r="E6" t="n">
-        <v>16.78157</v>
+        <v>16.36289</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95716</v>
+        <v>21.69328</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35278</v>
+        <v>34.72187</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.78311</v>
+        <v>16.93331</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00188</v>
+        <v>16.35977</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38981</v>
+        <v>16.67836</v>
       </c>
       <c r="F7" t="n">
-        <v>22.47707</v>
+        <v>21.67226</v>
       </c>
       <c r="G7" t="n">
-        <v>34.6269</v>
+        <v>34.77172</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.96355</v>
+        <v>16.62385</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1202</v>
+        <v>16.46198</v>
       </c>
       <c r="E8" t="n">
-        <v>16.56373</v>
+        <v>16.57206</v>
       </c>
       <c r="F8" t="n">
-        <v>21.72691</v>
+        <v>22.29412</v>
       </c>
       <c r="G8" t="n">
-        <v>33.99658</v>
+        <v>34.31326</v>
       </c>
     </row>
   </sheetData>
